--- a/artfynd/A 9019-2024 artfynd.xlsx
+++ b/artfynd/A 9019-2024 artfynd.xlsx
@@ -1728,11 +1728,11 @@
         <v>115967858</v>
       </c>
       <c r="B11" t="n">
-        <v>57271</v>
+        <v>57363</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">

--- a/artfynd/A 9019-2024 artfynd.xlsx
+++ b/artfynd/A 9019-2024 artfynd.xlsx
@@ -1980,11 +1980,11 @@
         <v>115967346</v>
       </c>
       <c r="B13" t="n">
-        <v>57281</v>
+        <v>57390</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2107,11 +2107,11 @@
         <v>115964695</v>
       </c>
       <c r="B14" t="n">
-        <v>57281</v>
+        <v>57390</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">

--- a/artfynd/A 9019-2024 artfynd.xlsx
+++ b/artfynd/A 9019-2024 artfynd.xlsx
@@ -1980,7 +1980,7 @@
         <v>115967346</v>
       </c>
       <c r="B13" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>115964695</v>
       </c>
       <c r="B14" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 9019-2024 artfynd.xlsx
+++ b/artfynd/A 9019-2024 artfynd.xlsx
@@ -1995,11 +1995,6 @@
       <c r="E13" t="n">
         <v>100049</v>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>
@@ -2121,11 +2116,6 @@
       </c>
       <c r="E14" t="n">
         <v>100049</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>

--- a/artfynd/A 9019-2024 artfynd.xlsx
+++ b/artfynd/A 9019-2024 artfynd.xlsx
@@ -1980,7 +1980,7 @@
         <v>115967346</v>
       </c>
       <c r="B13" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1994,6 +1994,11 @@
       </c>
       <c r="E13" t="n">
         <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2102,7 +2107,7 @@
         <v>115964695</v>
       </c>
       <c r="B14" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2116,6 +2121,11 @@
       </c>
       <c r="E14" t="n">
         <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>

--- a/artfynd/A 9019-2024 artfynd.xlsx
+++ b/artfynd/A 9019-2024 artfynd.xlsx
@@ -1980,7 +1980,7 @@
         <v>115967346</v>
       </c>
       <c r="B13" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>115964695</v>
       </c>
       <c r="B14" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 9019-2024 artfynd.xlsx
+++ b/artfynd/A 9019-2024 artfynd.xlsx
@@ -1980,7 +1980,7 @@
         <v>115967346</v>
       </c>
       <c r="B13" t="n">
-        <v>57400</v>
+        <v>57494</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>115964695</v>
       </c>
       <c r="B14" t="n">
-        <v>57400</v>
+        <v>57494</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
